--- a/Documents/Taches.xlsx
+++ b/Documents/Taches.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 Download 2\Cours\Session-6\__Les_projets\__Projet_Jeux_videos\Projet1_Jeux_Video\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chacy\My Shit\Projet1_Jeux_Video\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2154A493-2E88-4AE1-8322-000D87AE053B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57066389-FF95-47E9-9DF2-5068CA0985FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="58">
   <si>
     <t>Fonctionnalites</t>
   </si>
@@ -290,9 +290,6 @@
     <t>Commentaires</t>
   </si>
   <si>
-    <t>En cours</t>
-  </si>
-  <si>
     <t>Pas commencé</t>
   </si>
   <si>
@@ -312,15 +309,6 @@
   </si>
   <si>
     <t>tout le monde</t>
-  </si>
-  <si>
-    <t>Reste a exploser quand entre en contact avec un enemi</t>
-  </si>
-  <si>
-    <t>Reste a exploser quand entre en contact avec un enemi + weird starting position</t>
-  </si>
-  <si>
-    <t>Reste a exploser quand entre en contact avec un enemi + finir seekEnemy</t>
   </si>
   <si>
     <t>Terminé</t>
@@ -902,16 +890,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B5B6CB-DB26-432C-9FC7-91B77E13F469}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.1796875" customWidth="1"/>
-    <col min="2" max="2" width="106.453125" customWidth="1"/>
-    <col min="3" max="3" width="57.1796875" customWidth="1"/>
-    <col min="4" max="4" width="36.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="77.54296875" style="24" customWidth="1"/>
+    <col min="1" max="1" width="41.140625" customWidth="1"/>
+    <col min="2" max="2" width="106.42578125" customWidth="1"/>
+    <col min="3" max="3" width="57.140625" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77.5703125" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="55.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="55.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -928,7 +916,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="323.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="323.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -936,14 +924,14 @@
         <v>5</v>
       </c>
       <c r="C2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>52</v>
-      </c>
       <c r="E2" s="22"/>
     </row>
-    <row r="3" spans="1:5" ht="333" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5" ht="337.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -951,14 +939,14 @@
         <v>47</v>
       </c>
       <c r="C3" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>52</v>
-      </c>
       <c r="E3" s="23"/>
     </row>
-    <row r="4" spans="1:5" ht="56" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="57" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -966,14 +954,14 @@
         <v>8</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" s="22"/>
     </row>
-    <row r="5" spans="1:5" ht="59.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5" ht="59.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -981,14 +969,14 @@
         <v>10</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" spans="1:5" ht="220.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" ht="220.7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>12</v>
       </c>
@@ -996,16 +984,14 @@
         <v>11</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.5">
+        <v>52</v>
+      </c>
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1013,14 +999,14 @@
         <v>14</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" s="23"/>
     </row>
-    <row r="8" spans="1:5" ht="56" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5" ht="57" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1028,16 +1014,14 @@
         <v>16</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.5">
+        <v>52</v>
+      </c>
+      <c r="E8" s="22"/>
+    </row>
+    <row r="9" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -1045,16 +1029,14 @@
         <v>18</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="56" x14ac:dyDescent="0.5">
+        <v>52</v>
+      </c>
+      <c r="E9" s="22"/>
+    </row>
+    <row r="10" spans="1:5" ht="57" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1062,14 +1044,14 @@
         <v>20</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="22"/>
     </row>
-    <row r="11" spans="1:5" ht="112.5" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:5" ht="132.75" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
@@ -1077,14 +1059,14 @@
         <v>22</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>48</v>
       </c>
       <c r="E11" s="23"/>
     </row>
-    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>23</v>
       </c>
@@ -1092,14 +1074,14 @@
         <v>24</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>48</v>
       </c>
       <c r="E12" s="22"/>
     </row>
-    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1107,14 +1089,14 @@
         <v>26</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>48</v>
       </c>
       <c r="E13" s="23"/>
     </row>
-    <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -1122,14 +1104,14 @@
         <v>28</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>48</v>
       </c>
       <c r="E14" s="22"/>
     </row>
-    <row r="15" spans="1:5" ht="38.5" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:5" ht="57.75" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
@@ -1137,14 +1119,14 @@
         <v>30</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>48</v>
       </c>
       <c r="E15" s="23"/>
     </row>
-    <row r="16" spans="1:5" ht="57" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:5" ht="57.75" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
         <v>31</v>
       </c>
@@ -1152,14 +1134,14 @@
         <v>32</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>48</v>
       </c>
       <c r="E16" s="22"/>
     </row>
-    <row r="17" spans="1:6" ht="36" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:6" ht="39" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>33</v>
       </c>
@@ -1167,14 +1149,14 @@
         <v>34</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>48</v>
       </c>
       <c r="E17" s="23"/>
     </row>
-    <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>35</v>
       </c>
@@ -1182,14 +1164,14 @@
         <v>36</v>
       </c>
       <c r="C18" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>52</v>
-      </c>
       <c r="E18" s="22"/>
     </row>
-    <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>37</v>
       </c>
@@ -1197,14 +1179,14 @@
         <v>38</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" s="23"/>
     </row>
-    <row r="20" spans="1:6" ht="55.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1212,11 +1194,11 @@
         <v>40</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E20" s="22"/>
     </row>
-    <row r="21" spans="1:6" ht="74" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" ht="75" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>41</v>
       </c>
@@ -1224,14 +1206,14 @@
         <v>42</v>
       </c>
       <c r="C21" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>52</v>
-      </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" spans="1:6" ht="55.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1239,19 +1221,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="82.4" customHeight="1" x14ac:dyDescent="0.45">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="82.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>45</v>
       </c>
@@ -1259,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" s="8"/>
     </row>

--- a/Documents/Taches.xlsx
+++ b/Documents/Taches.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chacy\My Shit\Projet1_Jeux_Video\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\Projet1_Jeux_Video\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57066389-FF95-47E9-9DF2-5068CA0985FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF794A21-7105-4B53-8F34-AC39B9AA0D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BCE4F66-BD57-4DA1-9203-FCE236D7FCD6}"/>
   </bookViews>
@@ -924,7 +924,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>51</v>
@@ -939,7 +939,7 @@
         <v>47</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>51</v>
@@ -1164,7 +1164,7 @@
         <v>36</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>51</v>
@@ -1206,7 +1206,7 @@
         <v>42</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>51</v>
